--- a/analysis/data/annotation/[Archived] Labeling SDG 7 - Benchmarking Dataset.xlsx
+++ b/analysis/data/annotation/[Archived] Labeling SDG 7 - Benchmarking Dataset.xlsx
@@ -19,7 +19,6 @@
     <sheet state="hidden" name="sdg-mapper" sheetId="14" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="9" name="_xlnm._FilterDatabase">'Final Review'!$A$1:$I$101</definedName>
     <definedName hidden="1" localSheetId="11" name="_xlnm._FilterDatabase">Comparison!$A$1:$U$101</definedName>
     <definedName hidden="1" localSheetId="13" name="_xlnm._FilterDatabase">'sdg-mapper'!$A$1:$D$101</definedName>
   </definedNames>
@@ -1889,7 +1888,42 @@
 </file>
 
 <file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="8058150" cy="4324350"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="606399779" name="Chart1" title="Chart">
+          <a:extLst>
+            <a:ext uri="GoogleSheetsCustomDataVersion1">
+              <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" pictureOfChart="1"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2548,7 +2582,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="2" hidden="1">
+    <row r="2">
       <c r="A2" s="21" t="s">
         <v>162</v>
       </c>
@@ -2579,7 +2613,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" hidden="1">
+    <row r="3">
       <c r="A3" s="21" t="s">
         <v>165</v>
       </c>
@@ -2610,7 +2644,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" hidden="1">
+    <row r="4">
       <c r="A4" s="21" t="s">
         <v>303</v>
       </c>
@@ -2641,7 +2675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" hidden="1">
+    <row r="5">
       <c r="A5" s="21" t="s">
         <v>117</v>
       </c>
@@ -2672,7 +2706,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" hidden="1">
+    <row r="6">
       <c r="A6" s="21" t="s">
         <v>147</v>
       </c>
@@ -2703,7 +2737,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" hidden="1">
+    <row r="7">
       <c r="A7" s="21" t="s">
         <v>318</v>
       </c>
@@ -2734,7 +2768,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" hidden="1">
+    <row r="8">
       <c r="A8" s="21" t="s">
         <v>331</v>
       </c>
@@ -2765,7 +2799,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" hidden="1">
+    <row r="9">
       <c r="A9" s="21" t="s">
         <v>249</v>
       </c>
@@ -2796,7 +2830,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" hidden="1">
+    <row r="10">
       <c r="A10" s="21" t="s">
         <v>190</v>
       </c>
@@ -2827,7 +2861,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" hidden="1">
+    <row r="11">
       <c r="A11" s="21" t="s">
         <v>221</v>
       </c>
@@ -2858,7 +2892,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" hidden="1">
+    <row r="12">
       <c r="A12" s="21" t="s">
         <v>193</v>
       </c>
@@ -2889,7 +2923,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" hidden="1">
+    <row r="13">
       <c r="A13" s="21" t="s">
         <v>172</v>
       </c>
@@ -2920,7 +2954,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" hidden="1">
+    <row r="14">
       <c r="A14" s="21" t="s">
         <v>235</v>
       </c>
@@ -2951,7 +2985,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" hidden="1">
+    <row r="15">
       <c r="A15" s="21" t="s">
         <v>309</v>
       </c>
@@ -2982,7 +3016,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" hidden="1">
+    <row r="16">
       <c r="A16" s="21" t="s">
         <v>301</v>
       </c>
@@ -3013,7 +3047,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" hidden="1">
+    <row r="17">
       <c r="A17" s="21" t="s">
         <v>170</v>
       </c>
@@ -3044,7 +3078,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" hidden="1">
+    <row r="18">
       <c r="A18" s="21" t="s">
         <v>233</v>
       </c>
@@ -3075,7 +3109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" hidden="1">
+    <row r="19">
       <c r="A19" s="21" t="s">
         <v>326</v>
       </c>
@@ -3106,7 +3140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" hidden="1">
+    <row r="20">
       <c r="A20" s="21" t="s">
         <v>287</v>
       </c>
@@ -3137,7 +3171,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" hidden="1">
+    <row r="21">
       <c r="A21" s="21" t="s">
         <v>167</v>
       </c>
@@ -3168,7 +3202,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" hidden="1">
+    <row r="22">
       <c r="A22" s="21" t="s">
         <v>218</v>
       </c>
@@ -3199,7 +3233,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" hidden="1">
+    <row r="23">
       <c r="A23" s="21" t="s">
         <v>210</v>
       </c>
@@ -3230,7 +3264,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" hidden="1">
+    <row r="24">
       <c r="A24" s="21" t="s">
         <v>97</v>
       </c>
@@ -3261,7 +3295,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" hidden="1">
+    <row r="25">
       <c r="A25" s="21" t="s">
         <v>247</v>
       </c>
@@ -3292,7 +3326,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" hidden="1">
+    <row r="26">
       <c r="A26" s="21" t="s">
         <v>260</v>
       </c>
@@ -3323,7 +3357,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" hidden="1">
+    <row r="27">
       <c r="A27" s="21" t="s">
         <v>103</v>
       </c>
@@ -3354,7 +3388,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" hidden="1">
+    <row r="28">
       <c r="A28" s="21" t="s">
         <v>132</v>
       </c>
@@ -3385,7 +3419,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" hidden="1">
+    <row r="29">
       <c r="A29" s="21" t="s">
         <v>122</v>
       </c>
@@ -3416,7 +3450,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" hidden="1">
+    <row r="30">
       <c r="A30" s="21" t="s">
         <v>185</v>
       </c>
@@ -3447,7 +3481,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" hidden="1">
+    <row r="31">
       <c r="A31" s="21" t="s">
         <v>240</v>
       </c>
@@ -3478,7 +3512,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" hidden="1">
+    <row r="32">
       <c r="A32" s="21" t="s">
         <v>338</v>
       </c>
@@ -3509,7 +3543,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" hidden="1">
+    <row r="33">
       <c r="A33" s="21" t="s">
         <v>94</v>
       </c>
@@ -3540,7 +3574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" hidden="1">
+    <row r="34">
       <c r="A34" s="21" t="s">
         <v>263</v>
       </c>
@@ -3571,7 +3605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" hidden="1">
+    <row r="35">
       <c r="A35" s="21" t="s">
         <v>120</v>
       </c>
@@ -3602,7 +3636,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" hidden="1">
+    <row r="36">
       <c r="A36" s="21" t="s">
         <v>213</v>
       </c>
@@ -3633,7 +3667,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" hidden="1">
+    <row r="37">
       <c r="A37" s="21" t="s">
         <v>277</v>
       </c>
@@ -3664,7 +3698,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" hidden="1">
+    <row r="38">
       <c r="A38" s="21" t="s">
         <v>227</v>
       </c>
@@ -3695,7 +3729,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" hidden="1">
+    <row r="39">
       <c r="A39" s="21" t="s">
         <v>256</v>
       </c>
@@ -3726,7 +3760,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" hidden="1">
+    <row r="40">
       <c r="A40" s="21" t="s">
         <v>195</v>
       </c>
@@ -3757,7 +3791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" hidden="1">
+    <row r="41">
       <c r="A41" s="21" t="s">
         <v>208</v>
       </c>
@@ -3788,7 +3822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" hidden="1">
+    <row r="42">
       <c r="A42" s="21" t="s">
         <v>253</v>
       </c>
@@ -3819,7 +3853,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" hidden="1">
+    <row r="43">
       <c r="A43" s="21" t="s">
         <v>274</v>
       </c>
@@ -3850,7 +3884,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" hidden="1">
+    <row r="44">
       <c r="A44" s="21" t="s">
         <v>279</v>
       </c>
@@ -3881,7 +3915,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" hidden="1">
+    <row r="45">
       <c r="A45" s="21" t="s">
         <v>314</v>
       </c>
@@ -3912,7 +3946,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" hidden="1">
+    <row r="46">
       <c r="A46" s="21" t="s">
         <v>109</v>
       </c>
@@ -3943,7 +3977,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" hidden="1">
+    <row r="47">
       <c r="A47" s="21" t="s">
         <v>336</v>
       </c>
@@ -3974,7 +4008,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" hidden="1">
+    <row r="48">
       <c r="A48" s="21" t="s">
         <v>156</v>
       </c>
@@ -4005,7 +4039,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" hidden="1">
+    <row r="49">
       <c r="A49" s="21" t="s">
         <v>175</v>
       </c>
@@ -4036,7 +4070,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" hidden="1">
+    <row r="50">
       <c r="A50" s="21" t="s">
         <v>321</v>
       </c>
@@ -4067,7 +4101,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" hidden="1">
+    <row r="51">
       <c r="A51" s="21" t="s">
         <v>295</v>
       </c>
@@ -4098,7 +4132,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" hidden="1">
+    <row r="52">
       <c r="A52" s="21" t="s">
         <v>204</v>
       </c>
@@ -4129,7 +4163,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" hidden="1">
+    <row r="53">
       <c r="A53" s="21" t="s">
         <v>311</v>
       </c>
@@ -4160,7 +4194,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" hidden="1">
+    <row r="54">
       <c r="A54" s="21" t="s">
         <v>334</v>
       </c>
@@ -4191,7 +4225,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" hidden="1">
+    <row r="55">
       <c r="A55" s="21" t="s">
         <v>290</v>
       </c>
@@ -4222,7 +4256,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" hidden="1">
+    <row r="56">
       <c r="A56" s="21" t="s">
         <v>258</v>
       </c>
@@ -4253,7 +4287,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" hidden="1">
+    <row r="57">
       <c r="A57" s="21" t="s">
         <v>299</v>
       </c>
@@ -4284,7 +4318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" hidden="1">
+    <row r="58">
       <c r="A58" s="21" t="s">
         <v>125</v>
       </c>
@@ -4315,7 +4349,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" hidden="1">
+    <row r="59">
       <c r="A59" s="21" t="s">
         <v>84</v>
       </c>
@@ -4346,7 +4380,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" hidden="1">
+    <row r="60">
       <c r="A60" s="21" t="s">
         <v>183</v>
       </c>
@@ -4377,7 +4411,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" hidden="1">
+    <row r="61">
       <c r="A61" s="21" t="s">
         <v>251</v>
       </c>
@@ -4408,7 +4442,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" hidden="1">
+    <row r="62">
       <c r="A62" s="21" t="s">
         <v>135</v>
       </c>
@@ -4439,7 +4473,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" hidden="1">
+    <row r="63">
       <c r="A63" s="21" t="s">
         <v>187</v>
       </c>
@@ -4470,7 +4504,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" hidden="1">
+    <row r="64">
       <c r="A64" s="21" t="s">
         <v>282</v>
       </c>
@@ -4501,7 +4535,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" hidden="1">
+    <row r="65">
       <c r="A65" s="21" t="s">
         <v>130</v>
       </c>
@@ -4532,7 +4566,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" hidden="1">
+    <row r="66">
       <c r="A66" s="21" t="s">
         <v>268</v>
       </c>
@@ -4563,7 +4597,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" hidden="1">
+    <row r="67">
       <c r="A67" s="21" t="s">
         <v>144</v>
       </c>
@@ -4594,7 +4628,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" hidden="1">
+    <row r="68">
       <c r="A68" s="21" t="s">
         <v>112</v>
       </c>
@@ -4625,7 +4659,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" hidden="1">
+    <row r="69">
       <c r="A69" s="21" t="s">
         <v>88</v>
       </c>
@@ -4656,7 +4690,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" hidden="1">
+    <row r="70">
       <c r="A70" s="21" t="s">
         <v>243</v>
       </c>
@@ -4687,7 +4721,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" hidden="1">
+    <row r="71">
       <c r="A71" s="21" t="s">
         <v>230</v>
       </c>
@@ -4718,7 +4752,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" hidden="1">
+    <row r="72">
       <c r="A72" s="21" t="s">
         <v>224</v>
       </c>
@@ -4749,7 +4783,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" hidden="1">
+    <row r="73">
       <c r="A73" s="21" t="s">
         <v>100</v>
       </c>
@@ -4780,7 +4814,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" hidden="1">
+    <row r="74">
       <c r="A74" s="21" t="s">
         <v>297</v>
       </c>
@@ -4811,7 +4845,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" hidden="1">
+    <row r="75">
       <c r="A75" s="21" t="s">
         <v>180</v>
       </c>
@@ -4842,7 +4876,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" hidden="1">
+    <row r="76">
       <c r="A76" s="21" t="s">
         <v>141</v>
       </c>
@@ -4873,7 +4907,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" hidden="1">
+    <row r="77">
       <c r="A77" s="21" t="s">
         <v>106</v>
       </c>
@@ -4904,7 +4938,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" hidden="1">
+    <row r="78">
       <c r="A78" s="21" t="s">
         <v>91</v>
       </c>
@@ -4935,7 +4969,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" hidden="1">
+    <row r="79">
       <c r="A79" s="21" t="s">
         <v>201</v>
       </c>
@@ -4966,7 +5000,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" hidden="1">
+    <row r="80">
       <c r="A80" s="21" t="s">
         <v>329</v>
       </c>
@@ -4997,7 +5031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" hidden="1">
+    <row r="81">
       <c r="A81" s="21" t="s">
         <v>284</v>
       </c>
@@ -5028,7 +5062,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" hidden="1">
+    <row r="82">
       <c r="A82" s="21" t="s">
         <v>206</v>
       </c>
@@ -5059,7 +5093,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="83" hidden="1">
+    <row r="83">
       <c r="A83" s="21" t="s">
         <v>128</v>
       </c>
@@ -5090,7 +5124,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" hidden="1">
+    <row r="84">
       <c r="A84" s="21" t="s">
         <v>153</v>
       </c>
@@ -5121,7 +5155,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" hidden="1">
+    <row r="85">
       <c r="A85" s="21" t="s">
         <v>272</v>
       </c>
@@ -5152,7 +5186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" hidden="1">
+    <row r="86">
       <c r="A86" s="21" t="s">
         <v>198</v>
       </c>
@@ -5183,7 +5217,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" hidden="1">
+    <row r="87">
       <c r="A87" s="21" t="s">
         <v>115</v>
       </c>
@@ -5214,7 +5248,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" hidden="1">
+    <row r="88">
       <c r="A88" s="21" t="s">
         <v>159</v>
       </c>
@@ -5245,7 +5279,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="89" hidden="1">
+    <row r="89">
       <c r="A89" s="21" t="s">
         <v>178</v>
       </c>
@@ -5276,7 +5310,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" hidden="1">
+    <row r="90">
       <c r="A90" s="21" t="s">
         <v>245</v>
       </c>
@@ -5307,7 +5341,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" hidden="1">
+    <row r="91">
       <c r="A91" s="21" t="s">
         <v>270</v>
       </c>
@@ -5338,7 +5372,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="92" hidden="1">
+    <row r="92">
       <c r="A92" s="21" t="s">
         <v>292</v>
       </c>
@@ -5369,7 +5403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" hidden="1">
+    <row r="93">
       <c r="A93" s="21" t="s">
         <v>340</v>
       </c>
@@ -13296,17 +13330,6 @@
       <c r="H1000" s="34"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$I$101">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="50.00%"/>
-        <filter val="33.33%"/>
-      </filters>
-    </filterColumn>
-    <sortState ref="A1:I101">
-      <sortCondition descending="1" ref="G1:G101"/>
-    </sortState>
-  </autoFilter>
   <conditionalFormatting sqref="C2:G126">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"SDG 7"</formula>
@@ -62020,7 +62043,7 @@
         <v>1.0</v>
       </c>
       <c r="H2" s="21" t="str">
-        <f t="shared" ref="H2:H101" si="1">CHOOSE(ROUNDDOWN(G2*4.999999)+1, "very hard", "hard", "medium", "easy", "very easy")</f>
+        <f t="shared" ref="H2:H101" si="1">CHOOSE(ROUNDDOWN(G2*4.999999,0)+1, "very hard", "hard", "medium", "easy", "very easy")</f>
         <v>very easy</v>
       </c>
       <c r="I2" s="14" t="str">
